--- a/output/pdf_financials_xlsx/WEED.xlsx
+++ b/output/pdf_financials_xlsx/WEED.xlsx
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004488</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004763</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000215</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.051101</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1991,16 +1991,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.024068</v>
+        <v>-0.028556</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.021393</v>
+        <v>-0.026156</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.932925</v>
+        <v>-0.93314</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.346461</v>
+        <v>-9.397562000000001</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-3.37</v>
@@ -2109,16 +2109,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.024068</v>
+        <v>-0.028556</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.021393</v>
+        <v>-0.026156</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.929636</v>
+        <v>-0.929851</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.333461</v>
+        <v>-9.384562000000001</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.114</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-393.5925554673264</v>
+        <v>-395.7474874027506</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-8.772344279077092</v>
@@ -76120,7 +76120,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -77274,7 +77274,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">

--- a/output/pdf_financials_xlsx/WEED.xlsx
+++ b/output/pdf_financials_xlsx/WEED.xlsx
@@ -2061,7 +2061,7 @@
         <v>0.003289</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.013</v>
+        <v>0.647</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>2.256</v>
@@ -2076,25 +2076,25 @@
         <v>21.51</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>51.297</v>
+        <v>125.013</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>56.204</v>
+        <v>127.118</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>34.805</v>
+        <v>110.941</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>24.458</v>
+        <v>80.033</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>24.8</v>
+        <v>53.176</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>21.596</v>
+        <v>43.118</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>17.447</v>
+        <v>36.473</v>
       </c>
     </row>
     <row r="29">
@@ -2118,7 +2118,7 @@
         <v>-0.929851</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.384562000000001</v>
+        <v>-8.750562</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.114</v>
@@ -2133,19 +2133,19 @@
         <v>-686.403</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1457.757</v>
+        <v>-1384.041</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1627.757</v>
+        <v>-1556.843</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-304.71</v>
+        <v>-228.574</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3289.862</v>
+        <v>-3234.287</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-650.995</v>
+        <v>-622.619</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-395.7474874027506</v>
+        <v>-369.01167309268</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-8.772344279077092</v>
@@ -2200,19 +2200,19 @@
         <v>-270.8441350900245</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-331.5902608125998</v>
+        <v>-314.8223717432545</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-268.0768052595694</v>
+        <v>-256.3979130366042</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-53.25105642294666</v>
+        <v>-39.94554484860559</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-729.6195838997917</v>
+        <v>-717.294261933329</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-189.2790477242727</v>
+        <v>-181.0286275855251</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -6072,43 +6072,43 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.003289</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.256</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.064</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>20.486</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>46.918</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>125.013</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>127.118</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>110.941</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>80.033</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>53.176</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>43.118</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>36.473</v>
       </c>
     </row>
     <row r="101">
@@ -6765,10 +6765,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -31380,7 +31380,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -31462,7 +31466,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -40338,7 +40342,11 @@
           <t>Depreciation of property, plant and equipment 13</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -40434,7 +40442,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -41002,7 +41010,11 @@
           <t>Proceeds on disposals of property and equipment</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -42150,7 +42162,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -42246,7 +42262,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -42914,7 +42930,11 @@
           <t>Proceeds on disposals of property and equipment</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -44054,7 +44074,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -44150,7 +44174,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -45666,7 +45690,11 @@
           <t>Proceeds on disposals of property and equipment</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -47002,7 +47030,11 @@
           <t>Depreciation of property, plant and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -47098,7 +47130,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -49204,7 +49236,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">

--- a/output/pdf_financials_xlsx/WEED.xlsx
+++ b/output/pdf_financials_xlsx/WEED.xlsx
@@ -1325,28 +1325,28 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3.496</v>
+        <v>0.126</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7.572</v>
+        <v>-2.703</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.392</v>
+        <v>-0.392</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-4.112</v>
+        <v>4.112</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>121.614</v>
+        <v>-121.614</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>13.141</v>
+        <v>-13.141</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>8.948</v>
+        <v>-8.948</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>4.774</v>
+        <v>-4.774</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0</v>
@@ -1559,7 +1559,7 @@
         <v>-3.496</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-2.703</v>
+        <v>-12.978</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-51.064</v>
@@ -1734,7 +1734,7 @@
         <v>-3.496</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-2.703</v>
+        <v>-12.978</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-51.064</v>
@@ -2249,10 +2249,10 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-103.7388724035608</v>
+        <v>-3.738872403560831</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-73.69343065693431</v>
+        <v>-26.30656934306569</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0.7618159203980099</v>
@@ -2319,7 +2319,7 @@
         <v>-27.5297267501378</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-6.775285123449054</v>
+        <v>-32.53039227973431</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-65.51034022681787</v>
@@ -3633,25 +3633,25 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>1141.673</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>1915.412</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>1297.127</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>1175.692</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>581.581</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>418.283</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>405.491</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>0</v>
@@ -3688,25 +3688,25 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>45.333</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>390.609</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>222.59</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>232.912</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>110.31</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>111.968</v>
       </c>
       <c r="Q57" s="3" t="n">
         <v>0</v>
@@ -4256,13 +4256,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>9.725</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>43.396</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>37.613</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>-3.496</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-2.703</v>
+        <v>-12.978</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-51.064</v>
@@ -6984,10 +6984,10 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.008919</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -6996,25 +6996,25 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-2.132</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-74.35899999999999</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-16.957</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-9.638999999999999</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-11.429</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-1.337</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.547</v>
       </c>
       <c r="P116" s="3" t="n">
         <v>0</v>
@@ -33592,7 +33592,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -34944,7 +34948,11 @@
           <t>Purchases of intangible assets</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -48282,7 +48290,11 @@
           <t>Purchases of intangible assets</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -50486,7 +50498,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -60000,7 +60016,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -74076,7 +74096,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E699" t="inlineStr">
         <is>
           <t>-</t>
